--- a/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -120,7 +120,7 @@
       <name val="阿里巴巴普惠体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="0000B050"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -839,7 +839,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -883,12 +883,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -907,7 +902,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -932,17 +927,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -970,7 +965,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -995,17 +990,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1014,7 +1009,12 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>fansilu</t>
+          <t>zhouyingying01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>樊思路</t>
+          <t>周莹莹</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>zhouyingying01</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>周莹莹</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1276,7 +1276,12 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1320,17 +1325,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>fansilu</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>樊思路</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1358,7 +1363,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1383,17 +1388,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zhangyali</t>
+          <t>wangchangfei</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>张亚丽</t>
+          <t>王常菲</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1426,7 +1431,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1456,12 +1461,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>zhangbiyu</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>张碧玉</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1470,7 +1475,12 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1489,7 +1499,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1514,17 +1524,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1533,7 +1543,12 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1552,7 +1567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1577,17 +1592,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1620,7 +1635,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1645,17 +1660,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>zhangyali</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>张亚丽</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1688,7 +1703,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1713,17 +1728,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>qinshunan</t>
+          <t>lijingzhe</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>秦淑楠</t>
+          <t>李京哲</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1732,12 +1747,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1756,7 +1766,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1781,17 +1791,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1824,7 +1834,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1849,17 +1859,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1868,7 +1878,12 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1917,12 +1932,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1955,7 +1970,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1980,17 +1995,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>wangchangfei</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>王常菲</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1999,12 +2014,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2023,7 +2033,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2048,17 +2058,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>魏新卓战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>zhangbiyu</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>张碧玉</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2067,12 +2077,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2096,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2174,13 +2179,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -2229,10 +2234,10 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -2258,32 +2263,6 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>魏新卓战队</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,7 +2296,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 7月23日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 7月24日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -2438,16 +2417,16 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>2</v>
@@ -2455,8 +2434,8 @@
       <c r="I4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="14" t="n">
-        <v>1</v>
+      <c r="J4" s="12" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="K4" s="13" t="n">
         <v>0.5</v>
@@ -2507,10 +2486,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>3</v>
@@ -2603,16 +2582,16 @@
       </c>
       <c r="C9" s="19" t="n"/>
       <c r="D9" s="20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>17</v>
@@ -2621,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="K9" s="21" t="n">
         <v>0.4705882352941176</v>
@@ -2640,16 +2619,16 @@
       </c>
       <c r="C10" s="19" t="inlineStr"/>
       <c r="D10" s="20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>17</v>
@@ -2658,7 +2637,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>0.4705882352941176</v>
@@ -2791,19 +2770,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2812,7 +2791,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -2837,24 +2816,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>荆雅博</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>jingyabo</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2863,7 +2842,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2914,7 +2893,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2939,24 +2918,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2965,7 +2944,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2990,24 +2969,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>李京哲</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>lijingzhe</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3016,7 +2995,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -3046,12 +3025,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3067,7 +3046,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -3097,19 +3076,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>樊思路</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>fansilu</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3118,7 +3097,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -3143,17 +3122,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>王常菲</t>
+          <t>张亚丽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>wangchangfei</t>
+          <t>zhangyali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3169,7 +3148,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -3194,24 +3173,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3220,7 +3199,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -3245,24 +3224,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>王常菲</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>wangchangfei</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3271,7 +3250,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -3296,17 +3275,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>周莹莹</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>zhouyingying01</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3322,7 +3301,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3347,24 +3326,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>张亚丽</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zhangyali</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3373,7 +3352,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -3403,19 +3382,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>周莹莹</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>zhouyingying01</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3424,7 +3403,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -3449,21 +3428,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>魏新卓战队</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>王娅宁</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>wangyaning</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -3475,7 +3454,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -3505,12 +3484,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>樊思路</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fansilu</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3526,7 +3505,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -3551,17 +3530,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3577,7 +3556,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3602,21 +3581,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>魏新卓战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>王娅宁</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>wangyaning</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3628,7 +3607,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -3653,24 +3632,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3679,7 +3658,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3704,17 +3683,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3730,7 +3709,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3842,7 +3821,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -3851,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H3" t="n">
         <v>0.5</v>

--- a/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,89 +42,44 @@
       <b val="1"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="阿里巴巴普惠体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="0000B050"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="阿里巴巴普惠体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="0000B050"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="阿里巴巴普惠体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -148,41 +103,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B14D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCC102"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEEAF6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F2FE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9E5F3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -270,63 +195,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,52 +219,29 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,11 +685,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -898,11 +748,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -927,17 +777,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>zhouyingying01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>周莹莹</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -946,7 +796,12 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -961,11 +816,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -990,17 +845,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1029,11 +884,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1058,17 +913,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1077,12 +932,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1097,11 +947,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1126,17 +976,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>zhouyingying01</t>
+          <t>zhangbiyu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>周莹莹</t>
+          <t>张碧玉</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1145,7 +995,12 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1160,11 +1015,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,17 +1044,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1228,11 +1083,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1257,17 +1112,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1276,11 +1131,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1296,11 +1151,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1325,17 +1180,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>fansilu</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>樊思路</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1344,7 +1199,12 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1359,11 +1219,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1388,17 +1248,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>wangchangfei</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>王常菲</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1407,12 +1267,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1427,11 +1282,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1456,17 +1311,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>zhangbiyu</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>张碧玉</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1475,12 +1330,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1495,11 +1345,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1524,17 +1374,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1563,11 +1413,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1592,17 +1442,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1631,11 +1481,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1660,17 +1510,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>zhangyali</t>
+          <t>fansilu</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>张亚丽</t>
+          <t>樊思路</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1679,12 +1529,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1699,11 +1544,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1728,17 +1573,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>yuxiaoyuan</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>禹骁原</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1747,7 +1592,12 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10,11,12,13</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1762,11 +1612,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1791,17 +1641,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>lijingzhe</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>李京哲</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1810,11 +1660,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1830,11 +1680,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1859,17 +1709,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>qinshunan</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>秦淑楠</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1878,12 +1728,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1898,11 +1743,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1927,17 +1772,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>zhangyali</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>张亚丽</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1966,11 +1811,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1995,17 +1840,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>zhumengcheng</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>朱梦成</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2014,7 +1859,12 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2029,11 +1879,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2063,12 +1913,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2077,14 +1927,150 @@
         </is>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>jingyabo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>荆雅博</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>wangchunjiu</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>汪春玖</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>爱学</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>小短</t>
         </is>
@@ -2101,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,17 +2187,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2227,17 +2213,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -2253,16 +2239,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>王梦迪战队</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2280,23 +2292,23 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.90384615384615" customWidth="1" min="1" max="1"/>
-    <col width="6.92307692307692" customWidth="1" min="2" max="2"/>
-    <col width="22.9807692307692" customWidth="1" min="3" max="3"/>
-    <col width="11.1057692307692" customWidth="1" min="4" max="4"/>
-    <col width="11.1634615384615" customWidth="1" min="5" max="5"/>
-    <col width="16.5673076923077" customWidth="1" min="6" max="6"/>
-    <col width="16.7307692307692" customWidth="1" min="7" max="7"/>
-    <col width="9.375" customWidth="1" min="8" max="8"/>
-    <col width="16.7307692307692" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="17.3076923076923" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 7月24日</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 8月9日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -2311,336 +2323,336 @@
       <c r="K1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>学部</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>年级</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>战队</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>低价课带班</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>全天在线</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>个微全天在线率</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>接流</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>授权人数</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>正常人数</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>爱芯个微授权率</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>个微功能正常率</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>仵夏炎战队</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" s="11" t="n">
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>吕志恒战队</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="12" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>吕志恒战队</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>朱梦成战队</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>全年级 汇总</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="11" t="n">
+      <c r="G9" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>李丹阳战队</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="9" t="n">
+      <c r="I9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="11" t="n">
+      <c r="J9" s="13" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="14" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>小学 汇总</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="13" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="14" t="n">
+      <c r="I10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="J10" s="13" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="K10" s="14" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>魏新卓战队</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="16" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>全年级 汇总</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>小学 汇总</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.4705882352941176</v>
       </c>
     </row>
   </sheetData>
@@ -2687,7 +2699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,12 +2725,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>老师邮箱</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>老师姓名</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>老师邮箱</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -2765,24 +2777,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>zhumengcheng</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>朱梦成</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2791,929 +2803,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>荆雅博</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>jingyabo</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>魏新卓战队</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>张碧玉</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>zhangbiyu</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>仵夏炎</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>wuxiayan</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>李京哲</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>lijingzhe</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>王欣冉</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>wangxinran</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>樊思路</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>fansilu</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>李丹阳战队</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>张亚丽</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>zhangyali</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>杨喜菊</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>yangxiju</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>王常菲</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>wangchangfei</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>吕志恒战队</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>吕志恒</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>lvzhiheng</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>李少辉</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>lishaohui</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>周莹莹</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>zhouyingying01</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>魏新卓战队</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>王娅宁</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>wangyaning</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>仵夏炎战队</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>陈湘茹</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>chenxiangru</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>李丹阳战队</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>李丹阳</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>lidanyang</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>王梦迪</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>wangmengdi01</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>张昱莹</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>zhangyuying01</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>小短</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>吕志恒战队</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>刘栋辉</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>liudonghui</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3792,16 +2886,13 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3824,16 +2915,13 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3849,23 +2937,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -3881,23 +2969,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3913,22 +2998,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3945,7 +3027,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>魏新卓战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,10 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -208,13 +212,10 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,6 +225,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1541,16 +1545,16 @@
         <v>3</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1567,23 +1571,23 @@
       <c r="E4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -1607,86 +1611,86 @@
         <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>0.5</v>
+      <c r="J5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>全年级 汇总</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>0</v>
+      <c r="H6" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>小学</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>小学 汇总</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0</v>
+      <c r="H7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
   </sheetData>
@@ -1733,58 +1737,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>学部</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>年级</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>战队</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>老师邮箱</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>老师姓名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>个微授权</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>整体正常</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>运营中心</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>日期</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -1796,51 +1800,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>小短</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>小学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jingyabo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>荆雅博</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>wangchunjiu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>汪春玖</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>wuxiayan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lishaohui</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>李少辉</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yangxiju</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>杨喜菊</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>王梦迪战队</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>wangmengdi01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>王梦迪</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>郑州</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>zhangyuying01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>张昱莹</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1920,13 +2230,16 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -1949,13 +2262,16 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1978,13 +2294,13 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>

--- a/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/小短/郑州-小短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -61,7 +61,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B050"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -219,6 +219,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -595,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,11 +695,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -721,17 +724,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +762,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -780,11 +783,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -809,17 +812,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -828,12 +831,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -847,12 +845,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -868,11 +866,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -897,17 +895,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -916,11 +914,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -935,12 +933,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -956,11 +954,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -985,17 +983,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1004,7 +1002,12 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>9,10,11,12</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1018,12 +1021,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1039,11 +1042,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1068,17 +1071,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1087,7 +1090,12 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1101,12 +1109,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1122,11 +1130,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1151,17 +1159,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>jingyabo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>荆雅博</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1189,12 +1197,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>jingyabo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>荆雅博</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1210,11 +1218,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1244,12 +1252,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>wangchunjiu</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>汪春玖</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1258,7 +1266,12 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1272,12 +1285,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>wangchunjiu</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>汪春玖</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1286,6 +1299,436 @@
         </is>
       </c>
       <c r="R8" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>peifang</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>裴芳</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>peifang</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>裴芳</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>lidanyang</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>李丹阳</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lidanyang</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>李丹阳</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>吕志恒战队</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>liudonghui</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>刘栋辉</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>liudonghui</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>刘栋辉</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>wuxiayan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>wuxiayan</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>小短</t>
         </is>
@@ -1302,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,13 +1797,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -1376,17 +1819,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1402,16 +1845,68 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>王梦迪战队</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1426,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1445,7 +1940,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 8月23日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（小短） 8月27日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -1529,26 +2024,26 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="9" t="n">
         <v>1</v>
@@ -1562,32 +2057,32 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.1666666666666667</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="5">
@@ -1595,7 +2090,7 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1614,93 +2109,192 @@
         <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>全年级 汇总</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="F9" s="12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>小学 汇总</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr"/>
-      <c r="D7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="C10" s="11" t="inlineStr"/>
+      <c r="D10" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>0.2857142857142857</v>
+      <c r="F10" s="12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>0.4166666666666667</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:F7">
+  <conditionalFormatting sqref="F3:F10">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1709,7 +2303,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J7">
+  <conditionalFormatting sqref="J3:J10">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1718,7 +2312,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K7">
+  <conditionalFormatting sqref="K3:K10">
     <cfRule type="dataBar" priority="3">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1737,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,7 +2394,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1820,24 +2414,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1851,7 +2445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1871,24 +2465,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>wangchunjiu</t>
+          <t>jingyabo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>汪春玖</t>
+          <t>荆雅博</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1902,7 +2496,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,17 +2516,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1953,7 +2547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1973,17 +2567,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2004,7 +2598,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2024,17 +2618,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2055,7 +2649,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2075,17 +2669,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2106,7 +2700,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2126,31 +2720,286 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>吕志恒战队</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>liudonghui</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>刘栋辉</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>吕志恒战队</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>lvzhiheng</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>吕志恒</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>lidanyang</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>李丹阳</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>王梦迪战队</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>wangmengdi01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>王梦迪</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>zhangyuying01</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>张昱莹</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>郑州</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K13" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2165,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,17 +3072,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -2255,23 +3104,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2287,7 +3133,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2297,12 +3143,108 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
     </row>
